--- a/streamlit/event_plan_workbook_builder/templates/copilot_input_template.xlsx
+++ b/streamlit/event_plan_workbook_builder/templates/copilot_input_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02.Company\02.CLOVE-LLC\02. Docomo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fnifh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92111E65-1FA2-4351-8F3E-1C9EB7A02985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B9432B-6C8E-4C98-A68E-FFC97C5BA8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>制約条件</t>
   </si>
@@ -146,23 +146,6 @@
     </r>
     <rPh sb="0" eb="3">
       <t>シセツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>除外対象フラグ</t>
-    </r>
-    <rPh sb="0" eb="4">
-      <t>ジョガイタイショウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -916,7 +899,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="4" t="s">
@@ -931,20 +914,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A323E914-30DF-4A5E-9143-855D07DBBD3B}">
-  <dimension ref="B2:G2"/>
+  <dimension ref="B2:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.625" style="6" customWidth="1"/>
     <col min="2" max="2" width="8.625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="6"/>
+    <col min="5" max="5" width="14.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
         <v>14</v>
       </c>
@@ -959,9 +941,6 @@
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -988,28 +967,28 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1032,13 +1011,13 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1058,10 +1037,10 @@
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.2">

--- a/streamlit/event_plan_workbook_builder/templates/copilot_input_template.xlsx
+++ b/streamlit/event_plan_workbook_builder/templates/copilot_input_template.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fnifh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B9432B-6C8E-4C98-A68E-FFC97C5BA8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217208A-B1B4-40FA-847E-23E794949908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="制約条件" sheetId="1" r:id="rId1"/>
-    <sheet name="施設別制約条件" sheetId="3" r:id="rId2"/>
-    <sheet name="施設別・日別_目標値" sheetId="4" r:id="rId3"/>
-    <sheet name="日付情報" sheetId="5" r:id="rId4"/>
-    <sheet name="アウトプットデータ形式" sheetId="6" r:id="rId5"/>
+    <sheet name="共通制約条件" sheetId="1" r:id="rId1"/>
+    <sheet name="支社別制約条件" sheetId="7" r:id="rId2"/>
+    <sheet name="施設別制約条件" sheetId="3" r:id="rId3"/>
+    <sheet name="施設別・日別_目標値" sheetId="4" r:id="rId4"/>
+    <sheet name="日付情報" sheetId="5" r:id="rId5"/>
+    <sheet name="アウトプットデータ形式" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>制約条件</t>
   </si>
@@ -194,30 +195,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>施設コード</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>施設名</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>PO</t>
     </r>
     <r>
@@ -347,6 +324,73 @@
   </si>
   <si>
     <t>インプットデータCPA水準</t>
+  </si>
+  <si>
+    <t>最小稼働ライン</t>
+  </si>
+  <si>
+    <t>最大稼働ライン</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>稼働曜日</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日当たり稼働ライン</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>支社名</t>
+    <rPh sb="0" eb="3">
+      <t>シシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>施設コード</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>施設名</t>
+    </r>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -473,21 +517,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -514,38 +543,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -827,84 +875,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:P17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="25.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="9.25" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B2" s="13"/>
+      <c r="C2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" s="3" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+      <c r="D3" s="15"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="16"/>
+      <c r="D6" s="15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="4" t="s">
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="15" t="s">
         <v>11</v>
       </c>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -913,35 +1011,120 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A323E914-30DF-4A5E-9143-855D07DBBD3B}">
-  <dimension ref="B2:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67E18C1-40EE-4739-8D84-5173E7B6EBEB}">
+  <dimension ref="B2:L13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="8.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="15.125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>17</v>
-      </c>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="18"/>
+      <c r="C4" s="9"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="18"/>
+      <c r="C5" s="9"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="18"/>
+      <c r="C6" s="9"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="18"/>
+      <c r="C7" s="9"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="18"/>
+      <c r="C8" s="9"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="18"/>
+      <c r="C9" s="9"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="18"/>
+      <c r="C10" s="9"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="18"/>
+      <c r="C11" s="9"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="18"/>
+      <c r="C12" s="9"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="18"/>
+      <c r="C13" s="9"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -950,45 +1133,33 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEBE991-43E5-49A9-9738-97659858A75A}">
-  <dimension ref="B2:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A323E914-30DF-4A5E-9143-855D07DBBD3B}">
+  <dimension ref="B2:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="16.625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>25</v>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -998,26 +1169,44 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2916EA3E-F780-4FF4-8772-49158B113C0B}">
-  <dimension ref="B2:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEBE991-43E5-49A9-9738-97659858A75A}">
+  <dimension ref="B2:I2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="5" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1027,123 +1216,152 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2916EA3E-F780-4FF4-8772-49158B113C0B}">
+  <dimension ref="B2:D2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3560EEDA-08D9-4C31-9B52-D78EC0B8D459}">
   <dimension ref="B2:AG5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="6" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>28</v>
+      <c r="C2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/streamlit/event_plan_workbook_builder/templates/copilot_input_template.xlsx
+++ b/streamlit/event_plan_workbook_builder/templates/copilot_input_template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217208A-B1B4-40FA-847E-23E794949908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="共通制約条件" sheetId="1" r:id="rId1"/>
